--- a/inventario/Inventario_Keiko.xlsx
+++ b/inventario/Inventario_Keiko.xlsx
@@ -1679,17 +1679,25 @@
       <c r="A15" s="9">
         <v>9</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>43</v>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>AFE-1507</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Filtro de combustible Advance AFE-1507</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Advance Filters</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Filtros</t>
+        </is>
       </c>
       <c r="F15" s="12">
         <v>5</v>
@@ -1701,36 +1709,78 @@
         <v>32</v>
       </c>
       <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q15" s="10"/>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Filtro de combustible Advance AFE-1507, catalogado para Hino FC Euro 3 y determinadas Isuzu FTR, FSR y FVR.</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Filtro de combustible Advance Filters AFE-1507. La ficha del distribuidor lo relaciona con Hino FC Euro 3 y determinadas aplicaciones Isuzu FTR, FSR y FVR. Antes de la entrega se confirma la referencia instalada, las conexiones y el motor. No se anuncian aplicaciones Mitsubishi ni años que la fuente no detalla.</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>Hino FC Euro 3: aplicación del distribuidor; confirmar motor y referencia instalada. | Isuzu FTR, FSR y FVR: determinadas aplicaciones; confirmar motor y referencia instalada.</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>MF-20780 (cruce del distribuidor; no identidad de marca) | Sakura F 1507 (cruce del distribuidor; comprobar conexiones y medidas)</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>https://distriparteslm.ec/producto/otr-afe-1507/</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="R15" s="10"/>
       <c r="S15" s="14"/>
       <c r="T15" s="11"/>
-      <c r="U15" s="8"/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>Código corregido de AFE-15017 a AFE-1507, confirmado en el empaque y autorizado por el taller el 1 de octubre de 2026. Una ficha comercial directa y etiqueta coincidente, sin confirmación de motor o VIN. No se trasladan precios, existencias, garantías o prestaciones del distribuidor al negocio. No se encontró respaldo para la aplicación Mitsubishi del nombre anterior.</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:21" ht="31.95" customHeight="1">
       <c r="A16" s="9">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>43</v>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>AF7864</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Filtro de aire Shogun AF7864</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>SHOGUN</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Filtros</t>
+        </is>
       </c>
       <c r="F16" s="12">
         <v>5</v>
@@ -1742,20 +1792,54 @@
         <v>32</v>
       </c>
       <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q16" s="10"/>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Filtro de aire Shogun Classic AF7864, relacionado por el distribuidor con Chevrolet LUV 2.2; confirmar versión.</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>Filtro de aire Shogun Classic AF7864, código visible en el empaque. MAXCAR lo incluye en una ficha Shogun/Sakura para LUV 2.2. Se comprueba la referencia del filtro instalado, la forma y las medidas antes de entregar. No se garantiza ajuste en todas las LUV ni se trasladan aplicaciones de otros fabricantes a esta pieza.</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>Chevrolet LUV 2.2: aplicación orientativa del distribuidor; confirmar versión, forma y medidas del filtro instalado.</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.maxcarsumegacentro.com/products/filtro-shogun-af7864-luv-2-2</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="R16" s="10"/>
       <c r="S16" s="14"/>
       <c r="T16" s="11"/>
-      <c r="U16" s="8"/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>Código corregido de AFT-7864 a AF7864, confirmado en el empaque y autorizado por el taller el 1 de octubre de 2026. El título comercial mezcla Shogun y Sakura. La marca y la línea Classic se leen en nuestra fotografía; la aplicación es orientativa. No se copia la lista extensa de equivalencias ni se presenta como medida comprobada del producto físico. No se traslada el precio del proveedor.</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:21" ht="31.95" customHeight="1">
       <c r="A17" s="9"/>
